--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104560676</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040984</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131021101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69623489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040391</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040986</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131040988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17009202</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56800537</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7116630</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/562885</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1882,8 +1942,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7116629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,6 +1945,118 @@
       <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/7116629</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136298543</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98170</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Haftahedarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6702633</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136298543</t>
         </is>
       </c>
     </row>
@@ -1962,6 +2074,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
